--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487036_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487036_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.477600000000001</v>
+        <v>8.938599999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.207100000000001</v>
+        <v>8.5075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2705</v>
+        <v>0.4311</v>
       </c>
       <c r="G2" t="n">
         <v>5.4999</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1454</v>
+        <v>0.3156</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.2251</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0701</v>
+        <v>0.0905</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7126</v>
+        <v>7.5054</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7806</v>
+        <v>5.6804</v>
       </c>
       <c r="F3" t="n">
-        <v>1.932</v>
+        <v>1.8249</v>
       </c>
       <c r="G3" t="n">
         <v>2.9205</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.115</v>
+        <v>-0.3222</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1322</v>
+        <v>0.0321</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2472</v>
+        <v>-0.3543</v>
       </c>
       <c r="V3" t="n">
         <v>2.784</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.6331</v>
+        <v>5.7923</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2857</v>
+        <v>5.2843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3474</v>
+        <v>0.508</v>
       </c>
       <c r="G4" t="n">
         <v>5.8089</v>
@@ -766,13 +766,13 @@
         <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5613</v>
+        <v>0.7205</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2249</v>
+        <v>1.2235</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6636</v>
+        <v>-0.503</v>
       </c>
       <c r="V4" t="n">
         <v>0.614</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.914</v>
+        <v>5.42</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3664</v>
+        <v>4.6685</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5476</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4707</v>
+        <v>5.1406</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3301</v>
+        <v>2.8421</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8008</v>
+        <v>2.2984</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4381</v>
+        <v>5.7611</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0776</v>
+        <v>3.0428</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3606</v>
+        <v>2.7183</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9674</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4076</v>
+        <v>-0.2006</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5598</v>
+        <v>-0.4199</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.965</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9301</v>
+        <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5387</v>
+        <v>0.8355</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0462</v>
+        <v>0.5516</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5849</v>
+        <v>0.2839</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8696</v>
+        <v>-0.9421</v>
       </c>
       <c r="W5" t="n">
-        <v>4.8696</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.2792</v>
+        <v>5.3726</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7686</v>
+        <v>4.0659</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5106000000000001</v>
+        <v>1.3067</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1406</v>
+        <v>1.4707</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8421</v>
+        <v>-0.3301</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2984</v>
+        <v>1.8008</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7611</v>
+        <v>2.4381</v>
       </c>
       <c r="K6" t="n">
-        <v>3.0428</v>
+        <v>0.0776</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7183</v>
+        <v>2.3606</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.9674</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2006</v>
+        <v>-0.4076</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4199</v>
+        <v>-0.5598</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3161</v>
+        <v>1.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6947</v>
+        <v>-0.0027</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6518</v>
+        <v>-0.3467</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0429</v>
+        <v>0.344</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9421</v>
+        <v>4.8696</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2859</v>
+        <v>4.8696</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.3798</v>
+        <v>4.5867</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6757</v>
+        <v>4.6114</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7041</v>
+        <v>-0.0247</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1374</v>
+        <v>5.2717</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0268</v>
+        <v>2.7355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1107</v>
+        <v>2.5362</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5841</v>
+        <v>5.5516</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7866</v>
+        <v>2.3285</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7976</v>
+        <v>3.2231</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4467</v>
+        <v>-0.28</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2402</v>
+        <v>0.4069</v>
       </c>
       <c r="O7" t="n">
         <v>-0.6869</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1231</v>
+        <v>0.965</v>
       </c>
       <c r="Q7" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.9301</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.1362</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.161</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.5138</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.1231</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2195</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1917</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.0277</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.8999</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.8999</v>
-      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.1128</v>
+        <v>4.2866</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1107</v>
+        <v>2.4754</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0021</v>
+        <v>1.8112</v>
       </c>
       <c r="G8" t="n">
-        <v>5.2717</v>
+        <v>1.1374</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7355</v>
+        <v>1.0268</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5362</v>
+        <v>0.1107</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5516</v>
+        <v>1.5841</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3285</v>
+        <v>0.7866</v>
       </c>
       <c r="L8" t="n">
-        <v>3.2231</v>
+        <v>0.7976</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.28</v>
+        <v>-0.4467</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4069</v>
+        <v>0.2402</v>
       </c>
       <c r="O8" t="n">
         <v>-0.6869</v>
       </c>
       <c r="P8" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9301</v>
+        <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6101</v>
+        <v>0.1262</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4759</v>
+        <v>-0.0086</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1342</v>
+        <v>0.1348</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5138</v>
+        <v>0.8999</v>
       </c>
       <c r="W8" t="n">
+        <v>0.8999</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.5138</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4.0778</v>
+        <v>3.6158</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4395</v>
+        <v>1.5396</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6383</v>
+        <v>2.0762</v>
       </c>
       <c r="G9" t="n">
         <v>2.2862</v>
@@ -1156,13 +1156,13 @@
         <v>2.5091</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4984</v>
+        <v>1.0364</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8302</v>
+        <v>0.9304</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6682</v>
+        <v>0.1061</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2859</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6996</v>
+        <v>1.341</v>
       </c>
       <c r="E10" t="n">
-        <v>0.665</v>
+        <v>1.0655</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0346</v>
+        <v>0.2755</v>
       </c>
       <c r="G10" t="n">
         <v>1.9874</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.967</v>
+        <v>-0.3255</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3569</v>
+        <v>0.0436</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6101</v>
+        <v>-0.3692</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0432</v>
+        <v>0.4705</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5849</v>
+        <v>-1.1843</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6281</v>
+        <v>1.6548</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6466</v>
@@ -1312,13 +1312,13 @@
         <v>2.8951</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0033</v>
+        <v>0.4306</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1943</v>
+        <v>0.2062</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1976</v>
+        <v>0.2244</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2436</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>46.34</v>
+        <v>46.3398</v>
       </c>
       <c r="E13" t="n">
-        <v>34.9278</v>
+        <v>34.9276</v>
       </c>
       <c r="F13" t="n">
-        <v>11.4122</v>
+        <v>11.4121</v>
       </c>
       <c r="G13" t="n">
         <v>28.4978</v>
       </c>
       <c r="H13" t="n">
-        <v>16.8913</v>
+        <v>16.89129999999999</v>
       </c>
       <c r="I13" t="n">
         <v>11.6065</v>
@@ -1459,7 +1459,7 @@
         <v>-6.233499999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>8.685300000000002</v>
+        <v>8.6853</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.5104</v>
@@ -1468,13 +1468,13 @@
         <v>22.196</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6044</v>
+        <v>2.604200000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5848</v>
+        <v>2.5846</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01950000000000002</v>
+        <v>0.0195999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>6.5524</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8954</v>
+        <v>-0.5553</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4079</v>
+        <v>1.5081</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3033</v>
+        <v>-2.0633</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4513</v>
@@ -1546,13 +1546,13 @@
         <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1811</v>
+        <v>0.159</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1652</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0159</v>
+        <v>0.2241</v>
       </c>
       <c r="V14" t="n">
         <v>-1.228</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.3447</v>
+        <v>-1.7918</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8428</v>
+        <v>-0.0585</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1875</v>
+        <v>-1.7334</v>
       </c>
       <c r="G15" t="n">
         <v>-2.8636</v>
@@ -1624,13 +1624,13 @@
         <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7615</v>
+        <v>0.3143</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2295</v>
+        <v>0.3282</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.468</v>
+        <v>-0.0139</v>
       </c>
       <c r="V15" t="n">
         <v>1.1435</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.3216</v>
+        <v>-2.3017</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8539</v>
+        <v>2.954</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.1754</v>
+        <v>-5.2557</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9863</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3655</v>
+        <v>-0.3457</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4032</v>
+        <v>-0.303</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0377</v>
+        <v>-0.0427</v>
       </c>
       <c r="V16" t="n">
         <v>-2.1278</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.5805</v>
+        <v>-3.5735</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4773</v>
+        <v>-1.6416</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.0578</v>
+        <v>-1.932</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5234</v>
+        <v>-4.063</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5288</v>
+        <v>-1.5411</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9946</v>
+        <v>-2.5219</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9681</v>
+        <v>-1.5067</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6415</v>
+        <v>-0.2122</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3267</v>
+        <v>-1.2945</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.4915</v>
+        <v>-2.5562</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.1702</v>
+        <v>-1.3288</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.3213</v>
+        <v>-1.2274</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.2811</v>
+        <v>0.772</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.8252</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3821</v>
+        <v>-0.2826</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2644</v>
+        <v>-0.1348</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1176</v>
+        <v>-0.1477</v>
       </c>
       <c r="V17" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0699</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.9473</v>
+        <v>-3.9414</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0421</v>
+        <v>0.277</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9052</v>
+        <v>-4.2184</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.063</v>
+        <v>-2.5234</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5411</v>
+        <v>-1.5288</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.5219</v>
+        <v>-0.9946</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5067</v>
+        <v>1.9681</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2122</v>
+        <v>0.6415</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2945</v>
+        <v>1.3267</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5562</v>
+        <v>-4.4915</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3288</v>
+        <v>-2.1702</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2274</v>
+        <v>-2.3213</v>
       </c>
       <c r="P18" t="n">
-        <v>0.772</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6564</v>
+        <v>0.0212</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5354</v>
+        <v>0.0641</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.121</v>
+        <v>-0.043</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.0699</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.4902</v>
+        <v>-5.7851</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0159</v>
+        <v>-1.3861</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.5061</v>
+        <v>-4.399</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7186</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6723</v>
+        <v>0.3774</v>
       </c>
       <c r="T19" t="n">
-        <v>2.135</v>
+        <v>0.7331</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4627</v>
+        <v>-0.3556</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.284800000000001</v>
+        <v>-7.3369</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.0045</v>
+        <v>-4.4036</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2803</v>
+        <v>-2.9333</v>
       </c>
       <c r="G20" t="n">
         <v>-4.2404</v>
@@ -2014,13 +2014,13 @@
         <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4158</v>
+        <v>-0.468</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0708</v>
+        <v>-0.4699</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3451</v>
+        <v>0.002</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6985</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.726800000000001</v>
+        <v>-7.8652</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9664</v>
+        <v>-2.666</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.7604</v>
+        <v>-5.1992</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9474</v>
@@ -2092,13 +2092,13 @@
         <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2003</v>
+        <v>-0.3387</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4032</v>
+        <v>-0.1028</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7972</v>
+        <v>-0.236</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4559</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-12.7487</v>
+        <v>-11.1861</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.9969</v>
+        <v>-5.9955</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.7518</v>
+        <v>-5.1906</v>
       </c>
       <c r="G22" t="n">
         <v>-6.7038</v>
@@ -2170,13 +2170,13 @@
         <v>1.7371</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6009</v>
+        <v>-0.0383</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0708</v>
+        <v>-0.0694</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5301</v>
+        <v>0.031</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1278</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-46.34</v>
+        <v>-44.337</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.4121</v>
+        <v>-11.4122</v>
       </c>
       <c r="F23" t="n">
-        <v>-34.9278</v>
+        <v>-32.92489999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-28.4978</v>
@@ -2239,7 +2239,7 @@
         <v>-17.84</v>
       </c>
       <c r="P23" t="n">
-        <v>-8.685500000000001</v>
+        <v>-8.685499999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-22.196</v>
@@ -2248,19 +2248,19 @@
         <v>13.5106</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.6041</v>
+        <v>-0.6013999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.01970000000000027</v>
+        <v>-0.01959999999999994</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.5847</v>
+        <v>-0.5818</v>
       </c>
       <c r="V23" t="n">
         <v>-6.5524</v>
       </c>
       <c r="W23" t="n">
-        <v>4.700699999999999</v>
+        <v>4.7007</v>
       </c>
       <c r="X23" t="n">
         <v>-11.2531</v>
